--- a/v1.2/A2PICO2.v1.2_CPL.xlsx
+++ b/v1.2/A2PICO2.v1.2_CPL.xlsx
@@ -8,15 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ralle\Documents\A2PICO2.v1.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA0567A-AEF2-44BE-B492-F2F774FAD964}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D114EAD5-C482-4E51-B0DE-B185E422EDBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -1333,7 +1344,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="2">
-        <v>119.212182</v>
+        <v>121.41</v>
       </c>
       <c r="C30" s="2">
         <v>-90.650682000000003</v>

--- a/v1.2/A2PICO2.v1.2_CPL.xlsx
+++ b/v1.2/A2PICO2.v1.2_CPL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ralle\Documents\A2PICO2.v1.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D114EAD5-C482-4E51-B0DE-B185E422EDBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55C7906F-996D-4060-9425-EFC0489D168A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1344,7 +1344,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="2">
-        <v>121.41</v>
+        <v>120.4</v>
       </c>
       <c r="C30" s="2">
         <v>-90.650682000000003</v>

--- a/v1.2/A2PICO2.v1.2_CPL.xlsx
+++ b/v1.2/A2PICO2.v1.2_CPL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ralle\Documents\A2PICO2.v1.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55C7906F-996D-4060-9425-EFC0489D168A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF9FEF4-437D-471A-BF45-F19221F546B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1094,16 +1094,16 @@
         <v>36</v>
       </c>
       <c r="B20" s="2">
-        <v>172.52699999999999</v>
+        <v>166.6748</v>
       </c>
       <c r="C20" s="2">
-        <v>-83.919449999999998</v>
+        <v>-98.272599999999997</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E20" s="2">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
@@ -1369,16 +1369,16 @@
         <v>43</v>
       </c>
       <c r="B31" s="2">
-        <v>165.14699999999999</v>
+        <v>164.49039999999999</v>
       </c>
       <c r="C31" s="2">
-        <v>-89.296949999999995</v>
+        <v>-88.366600000000005</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E31" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>

--- a/v1.2/A2PICO2.v1.2_CPL.xlsx
+++ b/v1.2/A2PICO2.v1.2_CPL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ralle\Documents\A2PICO2.v1.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF9FEF4-437D-471A-BF45-F19221F546B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{580893D1-169C-4A24-B9E8-1512046E0776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1372,7 +1372,7 @@
         <v>164.49039999999999</v>
       </c>
       <c r="C31" s="2">
-        <v>-88.366600000000005</v>
+        <v>-90.566000000000003</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>5</v>

--- a/v1.2/A2PICO2.v1.2_CPL.xlsx
+++ b/v1.2/A2PICO2.v1.2_CPL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ralle\Documents\A2PICO2.v1.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{580893D1-169C-4A24-B9E8-1512046E0776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A59C84C-9049-4831-8B36-877D69355AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="65">
   <si>
     <t>Designator</t>
   </si>
@@ -192,9 +192,6 @@
   </si>
   <si>
     <t>LED1</t>
-  </si>
-  <si>
-    <t>C24</t>
   </si>
   <si>
     <t>R11</t>
@@ -612,7 +609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M61"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="13.36328125" customWidth="1"/>
@@ -1216,19 +1213,19 @@
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="2" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>179.0446</v>
+        <v>135.60368199999999</v>
       </c>
       <c r="C25" s="2">
-        <v>-106.426</v>
+        <v>-104.40715</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E25" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
@@ -1241,19 +1238,19 @@
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="2" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="B26" s="2">
-        <v>135.60368199999999</v>
+        <v>140.30368200000001</v>
       </c>
       <c r="C26" s="2">
-        <v>-104.40715</v>
+        <v>-104.43255000000001</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E26" s="2">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
@@ -1266,10 +1263,10 @@
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B27" s="2">
-        <v>140.30368200000001</v>
+        <v>145.00268199999999</v>
       </c>
       <c r="C27" s="2">
         <v>-104.43255000000001</v>
@@ -1291,19 +1288,19 @@
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B28" s="2">
-        <v>145.00268199999999</v>
+        <v>149.04028199999999</v>
       </c>
       <c r="C28" s="2">
-        <v>-104.43255000000001</v>
+        <v>-102.5852</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E28" s="2">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
@@ -1316,13 +1313,13 @@
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="2" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="B29" s="2">
-        <v>149.04028199999999</v>
+        <v>120.4</v>
       </c>
       <c r="C29" s="2">
-        <v>-102.5852</v>
+        <v>-90.650682000000003</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>5</v>
@@ -1341,19 +1338,19 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="2" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B30" s="2">
-        <v>120.4</v>
+        <v>164.49039999999999</v>
       </c>
       <c r="C30" s="2">
-        <v>-90.650682000000003</v>
+        <v>-90.566000000000003</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E30" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
@@ -1366,19 +1363,19 @@
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B31" s="2">
-        <v>164.49039999999999</v>
+        <v>126.891482</v>
       </c>
       <c r="C31" s="2">
-        <v>-90.566000000000003</v>
+        <v>-86.852800000000002</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E31" s="2">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
@@ -1391,19 +1388,19 @@
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B32" s="2">
-        <v>126.891482</v>
+        <v>140.70898199999999</v>
       </c>
       <c r="C32" s="2">
-        <v>-86.852800000000002</v>
+        <v>-82.697000000000003</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E32" s="2">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
@@ -1416,21 +1413,20 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="2" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="B33" s="2">
-        <v>140.70898199999999</v>
+        <v>126.702282</v>
       </c>
       <c r="C33" s="2">
-        <v>-82.697000000000003</v>
+        <v>-91.117999999999995</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E33" s="2">
-        <v>180</v>
-      </c>
-      <c r="F33" s="3"/>
+        <v>0</v>
+      </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
@@ -1441,13 +1437,13 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B34" s="2">
         <v>126.702282</v>
       </c>
       <c r="C34" s="2">
-        <v>-91.117999999999995</v>
+        <v>-90.127399999999994</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>5</v>
@@ -1465,19 +1461,19 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B35" s="2">
-        <v>126.702282</v>
+        <v>126.974738</v>
       </c>
       <c r="C35" s="2">
-        <v>-90.127399999999994</v>
+        <v>-83.597800000000007</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E35" s="2">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
@@ -1488,19 +1484,19 @@
       <c r="M35" s="3"/>
     </row>
     <row r="36" spans="1:13">
-      <c r="A36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B36" s="2">
-        <v>126.974738</v>
-      </c>
-      <c r="C36" s="2">
-        <v>-83.597800000000007</v>
+      <c r="A36" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="4">
+        <v>145.57848200000001</v>
+      </c>
+      <c r="C36" s="4">
+        <v>-87.943954000000005</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36" s="4">
         <v>180</v>
       </c>
       <c r="G36" s="3"/>
@@ -1513,13 +1509,13 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B37" s="4">
-        <v>145.57848200000001</v>
+        <v>126.69533800000001</v>
       </c>
       <c r="C37" s="4">
-        <v>-87.943954000000005</v>
+        <v>-95.078599999999994</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>5</v>
@@ -1537,19 +1533,19 @@
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B38" s="4">
         <v>126.69533800000001</v>
       </c>
       <c r="C38" s="4">
-        <v>-95.078599999999994</v>
+        <v>-94.087999999999994</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E38" s="4">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
@@ -1561,13 +1557,13 @@
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B39" s="4">
-        <v>126.69533800000001</v>
+        <v>151.2687</v>
       </c>
       <c r="C39" s="4">
-        <v>-94.087999999999994</v>
+        <v>-89.789000000000001</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>5</v>
@@ -1585,13 +1581,13 @@
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B40" s="4">
         <v>151.2687</v>
       </c>
       <c r="C40" s="4">
-        <v>-89.789000000000001</v>
+        <v>-90.779600000000002</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>5</v>
@@ -1609,13 +1605,13 @@
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B41" s="4">
         <v>151.2687</v>
       </c>
       <c r="C41" s="4">
-        <v>-90.779600000000002</v>
+        <v>-91.770200000000003</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>5</v>
@@ -1633,13 +1629,13 @@
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B42" s="4">
         <v>151.2687</v>
       </c>
       <c r="C42" s="4">
-        <v>-91.770200000000003</v>
+        <v>-92.760800000000003</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>5</v>
@@ -1657,13 +1653,13 @@
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="4" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="B43" s="4">
         <v>151.2687</v>
       </c>
       <c r="C43" s="4">
-        <v>-92.760800000000003</v>
+        <v>-93.751400000000004</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>5</v>
@@ -1687,7 +1683,7 @@
         <v>151.2687</v>
       </c>
       <c r="C44" s="4">
-        <v>-93.751400000000004</v>
+        <v>-94.742000000000004</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>5</v>
@@ -1708,10 +1704,10 @@
         <v>54</v>
       </c>
       <c r="B45" s="4">
-        <v>151.2687</v>
+        <v>153.4571</v>
       </c>
       <c r="C45" s="4">
-        <v>-94.742000000000004</v>
+        <v>-89.789000000000001</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>5</v>
@@ -1732,10 +1728,10 @@
         <v>55</v>
       </c>
       <c r="B46" s="4">
-        <v>153.4571</v>
+        <v>153.45509999999999</v>
       </c>
       <c r="C46" s="4">
-        <v>-89.789000000000001</v>
+        <v>-90.779600000000002</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>5</v>
@@ -1759,7 +1755,7 @@
         <v>153.45509999999999</v>
       </c>
       <c r="C47" s="4">
-        <v>-90.779600000000002</v>
+        <v>-91.770200000000003</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>5</v>
@@ -1783,7 +1779,7 @@
         <v>153.45509999999999</v>
       </c>
       <c r="C48" s="4">
-        <v>-91.770200000000003</v>
+        <v>-92.760800000000003</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>5</v>
@@ -1807,7 +1803,7 @@
         <v>153.45509999999999</v>
       </c>
       <c r="C49" s="4">
-        <v>-92.760800000000003</v>
+        <v>-93.751400000000004</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>5</v>
@@ -1831,7 +1827,7 @@
         <v>153.45509999999999</v>
       </c>
       <c r="C50" s="4">
-        <v>-93.751400000000004</v>
+        <v>-94.742000000000004</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>5</v>
@@ -1852,16 +1848,16 @@
         <v>60</v>
       </c>
       <c r="B51" s="4">
-        <v>153.45509999999999</v>
+        <v>132.47948199999999</v>
       </c>
       <c r="C51" s="4">
-        <v>-94.742000000000004</v>
+        <v>-102.8522</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E51" s="4">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
@@ -1876,16 +1872,16 @@
         <v>61</v>
       </c>
       <c r="B52" s="4">
-        <v>132.47948199999999</v>
+        <v>137.87133800000001</v>
       </c>
       <c r="C52" s="4">
-        <v>-102.8522</v>
+        <v>-82.607200000000006</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E52" s="4">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
@@ -1900,16 +1896,16 @@
         <v>62</v>
       </c>
       <c r="B53" s="4">
-        <v>137.87133800000001</v>
+        <v>126.69533800000001</v>
       </c>
       <c r="C53" s="4">
-        <v>-82.607200000000006</v>
+        <v>-92.106800000000007</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E53" s="4">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
@@ -1927,7 +1923,7 @@
         <v>126.69533800000001</v>
       </c>
       <c r="C54" s="4">
-        <v>-92.106800000000007</v>
+        <v>-93.097399999999993</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>5</v>
@@ -1945,13 +1941,13 @@
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="4" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="B55" s="4">
-        <v>126.69533800000001</v>
+        <v>176.63159999999999</v>
       </c>
       <c r="C55" s="4">
-        <v>-93.097399999999993</v>
+        <v>-86.393600000000006</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>5</v>
@@ -1969,13 +1965,13 @@
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="4" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B56" s="4">
-        <v>176.63159999999999</v>
+        <v>152.47013799999999</v>
       </c>
       <c r="C56" s="4">
-        <v>-86.393600000000006</v>
+        <v>-86.321399999999997</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>5</v>
@@ -1993,19 +1989,19 @@
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B57" s="4">
-        <v>152.47013799999999</v>
+        <v>137.36795000000001</v>
       </c>
       <c r="C57" s="4">
-        <v>-86.321399999999997</v>
+        <v>-89.859753999999995</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E57" s="4">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
@@ -2017,19 +2013,19 @@
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="4" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="B58" s="4">
-        <v>137.36795000000001</v>
+        <v>154.66059999999999</v>
       </c>
       <c r="C58" s="4">
-        <v>-89.859753999999995</v>
+        <v>-105.3283</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E58" s="4">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
@@ -2041,19 +2037,19 @@
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="4" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="B59" s="4">
-        <v>154.66059999999999</v>
+        <v>129.432682</v>
       </c>
       <c r="C59" s="4">
-        <v>-105.3283</v>
+        <v>-103.42305</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E59" s="4">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
@@ -2065,19 +2061,19 @@
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="4" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="B60" s="4">
-        <v>129.432682</v>
+        <v>146.05000000000001</v>
       </c>
       <c r="C60" s="4">
-        <v>-103.42305</v>
+        <v>-91.516199999999998</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E60" s="4">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
@@ -2087,30 +2083,6 @@
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
     </row>
-    <row r="61" spans="1:13">
-      <c r="A61" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B61" s="4">
-        <v>146.05000000000001</v>
-      </c>
-      <c r="C61" s="4">
-        <v>-91.516199999999998</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E61" s="4">
-        <v>90</v>
-      </c>
-      <c r="G61" s="3"/>
-      <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
-      <c r="J61" s="3"/>
-      <c r="K61" s="3"/>
-      <c r="L61" s="3"/>
-      <c r="M61" s="3"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
